--- a/data/clean/xtT_statekey.xlsx
+++ b/data/clean/xtT_statekey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmcgreal\Documents\dissertation\survey\data\clean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC70D99-BA9C-43D1-8DD8-67AD069606AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E9614F-1ADF-48A2-AD19-DCFE4A848F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{16596BDC-B16F-4A7F-96D8-13EAED7D8B44}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{16596BDC-B16F-4A7F-96D8-13EAED7D8B44}"/>
   </bookViews>
   <sheets>
     <sheet name="allstates" sheetId="1" r:id="rId1"/>
@@ -42,14 +42,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t>PopID</t>
   </si>
   <si>
-    <t>NosaChinRow(s)</t>
-  </si>
-  <si>
     <t>State</t>
   </si>
   <si>
@@ -72,6 +69,99 @@
   </si>
   <si>
     <t>Chinook</t>
+  </si>
+  <si>
+    <t>NosaCoho Row(s)</t>
+  </si>
+  <si>
+    <t>NosaChin Row(s)</t>
+  </si>
+  <si>
+    <t>8 to 10</t>
+  </si>
+  <si>
+    <t>11 to 13</t>
+  </si>
+  <si>
+    <t>14 to 16</t>
+  </si>
+  <si>
+    <t>17 to 19</t>
+  </si>
+  <si>
+    <t>20 to 22</t>
+  </si>
+  <si>
+    <t>23 to 25</t>
+  </si>
+  <si>
+    <t>26 to 28</t>
+  </si>
+  <si>
+    <t>29 to 31</t>
+  </si>
+  <si>
+    <t>32 to 34</t>
+  </si>
+  <si>
+    <t>35 to 37</t>
+  </si>
+  <si>
+    <t>38 to 40</t>
+  </si>
+  <si>
+    <t>41 to 43</t>
+  </si>
+  <si>
+    <t>44 to 46</t>
+  </si>
+  <si>
+    <t>47 to 49</t>
+  </si>
+  <si>
+    <t>50 to 52</t>
+  </si>
+  <si>
+    <t>54 to 56</t>
+  </si>
+  <si>
+    <t>57 to 59</t>
+  </si>
+  <si>
+    <t>62 &amp; 63</t>
+  </si>
+  <si>
+    <t>66 to 68</t>
+  </si>
+  <si>
+    <t>69 to 71</t>
+  </si>
+  <si>
+    <t>Coho</t>
+  </si>
+  <si>
+    <t>Steelhead</t>
+  </si>
+  <si>
+    <t>NosaStel Row(s)</t>
+  </si>
+  <si>
+    <t>1 to 3</t>
+  </si>
+  <si>
+    <t>4 to 6</t>
+  </si>
+  <si>
+    <t>7 &amp; 8</t>
+  </si>
+  <si>
+    <t>9 to 11</t>
+  </si>
+  <si>
+    <t>18 &amp; 19</t>
+  </si>
+  <si>
+    <t>22 &amp; 23</t>
   </si>
 </sst>
 </file>
@@ -107,10 +197,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,183 +534,461 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09582399-39F8-423E-A344-1189651C14E0}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
+      <c r="B3" t="s">
+        <v>6</v>
       </c>
       <c r="C3">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E3">
+        <v>109</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>58</v>
+      </c>
+      <c r="J3">
+        <v>20</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>8</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
+      <c r="B4" t="s">
+        <v>5</v>
       </c>
       <c r="C4">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E4">
+        <v>111</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>59</v>
+      </c>
+      <c r="J4">
+        <v>21</v>
+      </c>
+      <c r="K4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>9</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
+      <c r="B5" t="s">
+        <v>4</v>
       </c>
       <c r="C5">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E5">
+        <v>112</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>60</v>
+      </c>
+      <c r="J5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>12</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E6">
+        <v>113</v>
+      </c>
+      <c r="F6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>64</v>
+      </c>
+      <c r="J6">
+        <v>24</v>
+      </c>
+      <c r="K6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>13</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E7">
+        <v>114</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>65</v>
+      </c>
+      <c r="J7">
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>221</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <v>3</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E8">
+        <v>130</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>66</v>
+      </c>
+      <c r="J8">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>223</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>3</v>
+      <c r="B9" t="s">
+        <v>2</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E9">
+        <v>132</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="I9">
+        <v>67</v>
+      </c>
+      <c r="J9">
+        <v>27</v>
+      </c>
+      <c r="K9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>230</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10">
         <v>8</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E10">
+        <v>133</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+      <c r="I10">
+        <v>68</v>
+      </c>
+      <c r="J10">
+        <v>28</v>
+      </c>
+      <c r="K10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>232</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11">
         <v>9</v>
       </c>
       <c r="C11">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E11">
+        <v>140</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11">
+        <v>9</v>
+      </c>
+      <c r="I11">
+        <v>70</v>
+      </c>
+      <c r="J11">
+        <v>29</v>
+      </c>
+      <c r="K11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>237</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12">
         <v>10</v>
       </c>
       <c r="C12">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E12">
+        <v>141</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>71</v>
+      </c>
+      <c r="J12">
+        <v>30</v>
+      </c>
+      <c r="K12">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>238</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13">
         <v>11</v>
       </c>
       <c r="C13">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E13">
+        <v>142</v>
+      </c>
+      <c r="F13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13">
+        <v>11</v>
+      </c>
+      <c r="I13">
+        <v>84</v>
+      </c>
+      <c r="J13">
+        <v>31</v>
+      </c>
+      <c r="K13">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>239</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E14">
+        <v>143</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14">
+        <v>12</v>
+      </c>
+      <c r="I14">
+        <v>85</v>
+      </c>
+      <c r="J14">
+        <v>32</v>
+      </c>
+      <c r="K14">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>244</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15">
         <v>14</v>
       </c>
       <c r="C15">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E15">
+        <v>145</v>
+      </c>
+      <c r="F15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15">
+        <v>13</v>
+      </c>
+      <c r="I15">
+        <v>304</v>
+      </c>
+      <c r="J15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>246</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E16">
+        <v>150</v>
+      </c>
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16">
+        <v>14</v>
+      </c>
+      <c r="I16">
+        <v>310</v>
+      </c>
+      <c r="J16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>247</v>
       </c>
@@ -631,8 +998,26 @@
       <c r="C17">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E17">
+        <v>151</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17">
+        <v>15</v>
+      </c>
+      <c r="I17">
+        <v>311</v>
+      </c>
+      <c r="J17" t="s">
+        <v>36</v>
+      </c>
+      <c r="K17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>248</v>
       </c>
@@ -642,8 +1027,26 @@
       <c r="C18">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E18">
+        <v>153</v>
+      </c>
+      <c r="F18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18">
+        <v>16</v>
+      </c>
+      <c r="I18">
+        <v>315</v>
+      </c>
+      <c r="J18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>250</v>
       </c>
@@ -653,8 +1056,26 @@
       <c r="C19">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E19">
+        <v>159</v>
+      </c>
+      <c r="F19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19">
+        <v>17</v>
+      </c>
+      <c r="I19">
+        <v>316</v>
+      </c>
+      <c r="J19">
+        <v>12</v>
+      </c>
+      <c r="K19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>251</v>
       </c>
@@ -664,8 +1085,26 @@
       <c r="C20">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E20">
+        <v>161</v>
+      </c>
+      <c r="F20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20">
+        <v>18</v>
+      </c>
+      <c r="I20">
+        <v>317</v>
+      </c>
+      <c r="J20">
+        <v>13</v>
+      </c>
+      <c r="K20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>504</v>
       </c>
@@ -675,8 +1114,26 @@
       <c r="C21">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E21">
+        <v>162</v>
+      </c>
+      <c r="F21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21">
+        <v>19</v>
+      </c>
+      <c r="I21">
+        <v>318</v>
+      </c>
+      <c r="J21">
+        <v>14</v>
+      </c>
+      <c r="K21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>505</v>
       </c>
@@ -686,8 +1143,26 @@
       <c r="C22">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E22">
+        <v>163</v>
+      </c>
+      <c r="F22">
+        <v>53</v>
+      </c>
+      <c r="G22">
+        <v>20</v>
+      </c>
+      <c r="I22">
+        <v>319</v>
+      </c>
+      <c r="J22">
+        <v>15</v>
+      </c>
+      <c r="K22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>506</v>
       </c>
@@ -696,6 +1171,130 @@
       </c>
       <c r="C23">
         <v>18</v>
+      </c>
+      <c r="E23">
+        <v>164</v>
+      </c>
+      <c r="F23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23">
+        <v>21</v>
+      </c>
+      <c r="I23">
+        <v>500</v>
+      </c>
+      <c r="J23">
+        <v>16</v>
+      </c>
+      <c r="K23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="E24">
+        <v>276</v>
+      </c>
+      <c r="F24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24">
+        <v>22</v>
+      </c>
+      <c r="I24">
+        <v>502</v>
+      </c>
+      <c r="J24">
+        <v>17</v>
+      </c>
+      <c r="K24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="E25">
+        <v>281</v>
+      </c>
+      <c r="F25">
+        <v>60</v>
+      </c>
+      <c r="G25">
+        <v>23</v>
+      </c>
+      <c r="I25">
+        <v>503</v>
+      </c>
+      <c r="J25" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="E26">
+        <v>282</v>
+      </c>
+      <c r="F26">
+        <v>61</v>
+      </c>
+      <c r="G26">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="E27">
+        <v>286</v>
+      </c>
+      <c r="F27" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="E28">
+        <v>287</v>
+      </c>
+      <c r="F28">
+        <v>64</v>
+      </c>
+      <c r="G28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="E29">
+        <v>288</v>
+      </c>
+      <c r="F29">
+        <v>65</v>
+      </c>
+      <c r="G29">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="E30">
+        <v>290</v>
+      </c>
+      <c r="F30" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="E31">
+        <v>292</v>
+      </c>
+      <c r="F31" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -713,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -894,7 +1493,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D9B9E7-B0D0-44EE-B625-C9C3B6A80B79}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -902,7 +1501,239 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>109</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>111</v>
+      </c>
+      <c r="B3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>112</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>113</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>114</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>130</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>132</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>133</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>140</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>141</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>142</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>143</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>145</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>150</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>151</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>153</v>
+      </c>
+      <c r="B17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>159</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>161</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>162</v>
+      </c>
+      <c r="B20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>163</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>164</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>276</v>
+      </c>
+      <c r="B23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>281</v>
+      </c>
+      <c r="B24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>282</v>
+      </c>
+      <c r="B25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>286</v>
+      </c>
+      <c r="B26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>287</v>
+      </c>
+      <c r="B27">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>288</v>
+      </c>
+      <c r="B28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>290</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>292</v>
+      </c>
+      <c r="B30">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -912,7 +1743,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB9CA9BB-6429-44B3-8EFA-9972E193A738}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -920,7 +1751,191 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>58</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>59</v>
+      </c>
+      <c r="B3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>60</v>
+      </c>
+      <c r="B4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>64</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>65</v>
+      </c>
+      <c r="B6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>66</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>67</v>
+      </c>
+      <c r="B8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>68</v>
+      </c>
+      <c r="B9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>70</v>
+      </c>
+      <c r="B10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>71</v>
+      </c>
+      <c r="B11">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>84</v>
+      </c>
+      <c r="B12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>85</v>
+      </c>
+      <c r="B13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>304</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>310</v>
+      </c>
+      <c r="B15">
         <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>311</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>315</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>316</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>317</v>
+      </c>
+      <c r="B19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>318</v>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>319</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>500</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>502</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>503</v>
+      </c>
+      <c r="B24">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/clean/xtT_statekey.xlsx
+++ b/data/clean/xtT_statekey.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmcgreal\Documents\dissertation\survey\data\clean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E9614F-1ADF-48A2-AD19-DCFE4A848F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F6F7F5-A0F8-49C0-9DF8-E7F432C9D207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{16596BDC-B16F-4A7F-96D8-13EAED7D8B44}"/>
+    <workbookView xWindow="-49650" yWindow="1635" windowWidth="14400" windowHeight="11745" activeTab="1" xr2:uid="{16596BDC-B16F-4A7F-96D8-13EAED7D8B44}"/>
   </bookViews>
   <sheets>
     <sheet name="allstates" sheetId="1" r:id="rId1"/>
@@ -1304,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{468A52F5-C9DE-4042-9969-15A9928FC725}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1333,7 +1333,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>221</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1357,7 +1357,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1365,7 +1365,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1373,7 +1373,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B11">
         <v>10</v>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B12">
         <v>11</v>
@@ -1405,7 +1405,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -1413,7 +1413,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B15">
         <v>14</v>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B16">
         <v>15</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>504</v>
+        <v>251</v>
       </c>
       <c r="B17">
         <v>16</v>
@@ -1445,7 +1445,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B19">
         <v>18</v>
@@ -1461,7 +1461,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>7</v>
+        <v>506</v>
       </c>
       <c r="B20">
         <v>19</v>
@@ -1469,7 +1469,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -1477,10 +1477,18 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22">
         <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>9</v>
+      </c>
+      <c r="B23">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/data/clean/xtT_statekey.xlsx
+++ b/data/clean/xtT_statekey.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmcgreal\Documents\dissertation\survey\data\clean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F6F7F5-A0F8-49C0-9DF8-E7F432C9D207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4563526-60BD-4A44-827D-D2880FC038A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-49650" yWindow="1635" windowWidth="14400" windowHeight="11745" activeTab="1" xr2:uid="{16596BDC-B16F-4A7F-96D8-13EAED7D8B44}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{16596BDC-B16F-4A7F-96D8-13EAED7D8B44}"/>
   </bookViews>
   <sheets>
     <sheet name="allstates" sheetId="1" r:id="rId1"/>
     <sheet name="chin" sheetId="2" r:id="rId2"/>
     <sheet name="coho" sheetId="3" r:id="rId3"/>
     <sheet name="stel" sheetId="4" r:id="rId4"/>
+    <sheet name="chinESU" sheetId="5" r:id="rId5"/>
+    <sheet name="cohoESU" sheetId="6" r:id="rId6"/>
+    <sheet name="stelESU" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
   <si>
     <t>PopID</t>
   </si>
@@ -162,16 +165,49 @@
   </si>
   <si>
     <t>22 &amp; 23</t>
+  </si>
+  <si>
+    <t>ESANAME</t>
+  </si>
+  <si>
+    <t>Lower Columbia River DPS</t>
+  </si>
+  <si>
+    <t>Upper Willamette River DPS</t>
+  </si>
+  <si>
+    <t>Middle Columbia River DPS</t>
+  </si>
+  <si>
+    <t>Snake River Basin DPS</t>
+  </si>
+  <si>
+    <t>Snake River spring/summer-run ESU</t>
+  </si>
+  <si>
+    <t>Lower Columbia River ESU</t>
+  </si>
+  <si>
+    <t>Upper Willamette River ESU</t>
+  </si>
+  <si>
+    <t>Oregon Coast ESU</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -197,9 +233,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1949,4 +1986,140 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44B3DF93-AD4F-4936-8069-88F6A55E6E93}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76E38C0-B5A9-406E-AC43-1BBCCAD12BCC}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C09928-B677-4F57-ABBA-F587CD684CC7}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>